--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext9" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext10" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext13" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROITABLE</t>
+          <t>ROI_TABLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -535,12 +537,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>STAR_TABLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -550,12 +552,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PIXEL_ROW</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C8" t="b">
@@ -565,7 +567,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PIXEL_COLUMN</t>
+          <t>PIXEL_ROW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -580,12 +582,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>PIXEL_COLUMN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -595,12 +597,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C11" t="b">
@@ -610,12 +612,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MODEL_IMAGE</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -625,15 +627,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>APERTURE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>CompImageHDU</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -648,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,17 +713,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -703,12 +735,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -748,14 +780,10 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -766,14 +794,10 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of dimension 2</t>
-        </is>
-      </c>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -789,7 +813,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -814,654 +838,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>PIXEL_COLUMN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>PIXEL_COLUMN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>7FfEA9cD0EcD79cD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TTYPE15</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>contamination</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>contamination</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TFORM15</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TTYPE16</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TFORM16</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TTYPE17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>total_in_aperture</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>total_in_aperture</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TFORM17</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2758256725</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1474,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1507,17 +937,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -1529,12 +959,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1551,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1574,10 +1004,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1588,116 +1022,736 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DPOS0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Change in position in Row from original WCS.</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPOS1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Change in position in Column from original WCS.</t>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>contamination</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>contamination</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>total_in_aperture</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>total_in_aperture</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>9SBYER9W9RAWCR9W</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1316192270</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1777,7 +1831,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1843,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -1812,10 +1866,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1826,1272 +1884,160 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRF_MODEL</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>DPOS0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Change in position in Row from original WCS.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>DPOS1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.76604444311898</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Change in position in Column from original WCS.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>DmXKFkWKDkWKDkWK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>4143738915</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PC2_2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-0.00021666666666666</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CDELT2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.00021666666666667</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CUNIT2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>RA---TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CTYPE2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DEC--TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>45.460998535156</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CRVAL2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-16.594999313354</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-16.594999313354</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A_ORDER</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A_0_0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3.37003854432842e-18</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A_0_1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-6.9785263260057e-20</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A_0_2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-3.9703987595512e-23</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A_0_3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>6.66363813187626e-25</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A_1_0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.6079633451011e-05</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A_1_1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-8.2922292375176e-07</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A_1_2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-3.3183151069542e-10</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A_2_0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-5.6509448985679e-23</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A_2_1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1.22485736636324e-24</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A_3_0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-3.6017523652885e-10</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B_ORDER</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B_0_0</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0.000151435005371086</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B_0_1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.000544760966309224</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B_0_2</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.36516576587348e-05</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B_0_3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.09338166521394e-10</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B_1_0</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.54376528535914e-18</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B_1_1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3.52359242917892e-20</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B_1_2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-2.4342035926037e-23</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B_2_0</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.44813947783169e-05</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B_2_1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7.88636107165082e-11</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B_3_0</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-1.4166460599018e-23</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AP_ORDER</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AP_0_0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-3.3700385443284e-18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AP_0_1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>6.9785263260057e-20</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AP_0_2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>3.97039875955128e-23</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AP_0_3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>-6.6636381318762e-25</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AP_1_0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.60796334510111e-05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AP_1_1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>8.29222923751763e-07</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AP_1_2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>3.31831510695423e-10</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AP_2_0</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>5.65094489856793e-23</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AP_2_1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-1.2248573663632e-24</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AP_3_0</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3.60175236528857e-10</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BP_ORDER</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BP_0_0</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-0.00015143500537108</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BP_0_1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>-0.00054476096630922</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-1.3651657658734e-05</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-1.0933816652139e-10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>-1.5437652853591e-18</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>-3.5235924291789e-20</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2.43420359260379e-23</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-1.4481394778316e-05</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-7.8863610716508e-11</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1.4166460599018e-23</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,12 +2107,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3183,12 +2129,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3206,7 +2152,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -3220,7 +2166,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -3228,131 +2174,1573 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IMSIZE0</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Size of the full detector image in ROW</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IMCRNR0</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Corner of the image in ROW.</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IMSIZE1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>-0.76604444311898</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Size of the full detector image in COLUMN</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IMCRNR1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.64278760968654</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Corner of the image in COLUMN.</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-0.64278760968654</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.76604444311898</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.00021666666666666</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.00021666666666667</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RA---TAN-SIP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEC--TAN-SIP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>45.460998535156</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-16.594999313354</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-16.594999313354</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A_ORDER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A_0_0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.37003854432842e-18</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A_0_1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-6.9785263260057e-20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A_0_2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-3.9703987595512e-23</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A_0_3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6.66363813187626e-25</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A_1_0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-1.6079633451011e-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A_1_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-8.2922292375176e-07</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A_1_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-3.3183151069542e-10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A_2_0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-5.6509448985679e-23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A_2_1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.22485736636324e-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A_3_0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-3.6017523652885e-10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B_ORDER</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B_0_0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.000151435005371086</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B_0_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.000544760966309224</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B_0_2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.36516576587348e-05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B_0_3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.09338166521394e-10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B_1_0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.54376528535914e-18</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B_1_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.52359242917892e-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B_1_2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-2.4342035926037e-23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B_2_0</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.44813947783169e-05</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B_2_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7.88636107165082e-11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B_3_0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-1.4166460599018e-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AP_ORDER</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AP_0_0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-3.3700385443284e-18</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AP_0_1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>6.9785263260057e-20</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AP_0_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.97039875955128e-23</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AP_0_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-6.6636381318762e-25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AP_1_0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.60796334510111e-05</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AP_1_1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8.29222923751763e-07</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AP_1_2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.31831510695423e-10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AP_2_0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5.65094489856793e-23</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AP_2_1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>-1.2248573663632e-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AP_3_0</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3.60175236528857e-10</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BP_ORDER</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BP_0_0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-0.00015143500537108</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BP_0_1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-0.00054476096630922</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BP_0_2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-1.3651657658734e-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BP_0_3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-1.0933816652139e-10</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BP_1_0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-1.5437652853591e-18</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BP_1_1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-3.5235924291789e-20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BP_1_2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2.43420359260379e-23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BP_2_0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>-1.4481394778316e-05</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BP_2_1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-7.8863610716508e-11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BP_3_0</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.4166460599018e-23</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>EXTNAME</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DCFJECEJDCEJDCEJ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3473186889</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NAXIS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>APERTURE</t>
@@ -3366,6 +3754,298 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAhkC0ekC7ekC7ek</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>44499607</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NAXIS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>electrons/pixel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data units: electrons/pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1CNi29Kg1CKg19Kg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3483260417</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -3380,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3517,11 +4197,7 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
@@ -3680,7 +4356,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3698,7 +4374,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3716,7 +4392,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/12/03/2025-12-03__17-33-11_VisSci_LTT_1445_d050_n009_f00050_e000200000us.sp</t>
+          <t>/sssp/data/2026/01/04/2026-01-04__14-54-31_VisSci_LTT_1445_A_d050_n026_f00050_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3752,7 +4428,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LTT_1445</t>
+          <t>LTT_1445_A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3842,7 +4518,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3914,7 +4590,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3932,7 +4608,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3950,7 +4626,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3968,7 +4644,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4004,7 +4680,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4058,7 +4734,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>818098418</t>
+          <t>820853698</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4076,7 +4752,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>907000000</t>
+          <t>503000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4094,12 +4770,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kchWlZZVkbfVkZZV</t>
+          <t>9YDJFX9H9XCHCX9H</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:54</t>
+          <t>HDU checksum updated 2026-01-07T16:22:31</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4793,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:54</t>
+          <t>data unit checksum updated 2026-01-07T16:22:31</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4820,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4156,13 +4832,13 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
+          <t>VISDALevel2HDUList</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4176,7 +4852,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -4190,7 +4866,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4204,7 +4880,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4218,7 +4894,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied flat.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4232,10 +4908,24 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4348,7 +5038,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4362,7 +5052,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -4442,100 +5132,88 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>BZERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COUNTS</t>
+          <t>2147483648</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>data title: raw pixel counts</t>
-        </is>
-      </c>
+          <t>2147483648</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>EIRaEHPYEHPaEHPY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data format: images of unsigned 32-bit integers</t>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TUNIT1</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>3451315978</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data units: count</t>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ZcIAZZ98ZbGAZZ95</t>
+          <t>electrons/pixel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:54</t>
+          <t>data units: electrons/pixel</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>118173844</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2025-12-31T11:13:54</t>
-        </is>
-      </c>
+          <t>0.4.2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5800,7 +6478,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5983,12 +6661,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ROITABLE</t>
+          <t>ROI_TABLE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ROITABLE</t>
+          <t>ROI_TABLE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6006,7 +6684,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6042,12 +6720,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D3AbF05aD0AaD03a</t>
+          <t>ZflUedlRZdlRddlR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:54</t>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6738,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1666207348</t>
+          <t>2007004370</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:54</t>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -6404,12 +7082,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HiULJiTIHiTIHiTI</t>
+          <t>DgMHEgJHDgJHDgJH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:54</t>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -6422,12 +7100,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2897460663</t>
+          <t>2899297478</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:54</t>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -6442,7 +7120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6814,36 +7492,486 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>SDETMETH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CigFFZZDCfdDCZZD</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:54</t>
+          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>ATAITIME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3013170411</t>
+          <t>820853698.503</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:54</t>
+          <t>TAI Time for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AIMMEAN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>101.395988</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Image Mean after sigma clipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AIMSTD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2.082717</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Image Standard Deviation after sigma clipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ATHRESH1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1st Star Detection Threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ATHRESH2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2nd Star Detection Threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AMINELLP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Minimum ellipticity threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AMAXELLP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maximum ellipticity threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AMINFLUX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Minimum flux threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AMAXFLUX</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Maximum flux threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AXAXFLIP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Was x-axis flipped for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ASCAL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.7804</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plate Scale for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ASCALRMS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.0005</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plate Scale RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AROT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>39.905</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rotation for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AROTRMS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rotation RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>45.46205</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Right Ascension for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ARARMS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>9.699e-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Right Ascension RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ADEC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-16.594716</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Declination for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ADECRMS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.00010624</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Declination RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AZERP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21.76</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Magnitude Zeropoint for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AZERPRMS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Magnitude Zeropoint RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AQUADS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Number of quads used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AVERTS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Number of quad sides used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APHSTARS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Number of photometric stars used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APOSTARS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Number of position stars used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>U1o8a0m6X0m6a0m6</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3343168083</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -6858,7 +7986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6891,17 +8019,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>ASCII table extension</t>
         </is>
       </c>
     </row>
@@ -6913,12 +8041,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6958,10 +8086,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6972,10 +8104,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6991,7 +8127,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -7016,35 +8152,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>xCen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>xCen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -7052,22 +8192,688 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TBCOL1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yCen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yCen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TBCOL2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>I50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TBCOL3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ellipticity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ellipticity</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TBCOL4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NumPix</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NumPix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>I40</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TBCOL5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CatalogRA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CatalogRA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TBCOL6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CatalogDec</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CatalogDec</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TBCOL7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CatalogMag</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CatalogMag</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TBCOL8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FittedRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FittedRA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TBCOL9</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FittedDec</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FittedDec</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TBCOL10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FittedMag</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FittedMag</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TBCOL11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CatalogStar</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CatalogStar</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TBCOL12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>EXTNAME</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>STAR_TABLE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>STAR_TABLE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>name of extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EUafHUZdEUadEUWd</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>912660790</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -7082,7 +8888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,17 +8943,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -7169,7 +8975,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -7182,10 +8988,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7196,10 +9006,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7240,22 +9054,94 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>BSCALE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>EXTNAME</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PIXEL_ROW</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PIXEL_ROW</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HCeLJ9ZJHAdJH9ZJ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215911647</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>
@@ -7270,7 +9156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7370,7 +9256,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -7384,7 +9270,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -7433,17 +9319,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PIXEL_COLUMN</t>
+          <t>PIXEL_ROW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PIXEL_COLUMN</t>
+          <t>PIXEL_ROW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6THB9T996TEA6T99</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2333931600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:32</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -866,12 +866,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7FfEA9cD0EcD79cD</t>
+          <t>7EcD79cD7EcD79cD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9SBYER9W9RAWCR9W</t>
+          <t>94LaA4La94LaA4La</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1316192270</t>
+          <t>3358544653</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DmXKFkWKDkWKDkWK</t>
+          <t>mCA9nA58mAA8mA38</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4143738915</t>
+          <t>2524035719</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DCFJECEJDCEJDCEJ</t>
+          <t>hZEikZ9hhZEhhZ9h</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3473186889</t>
+          <t>2048992434</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CAhkC0ekC7ekC7ek</t>
+          <t>B9emC7ejB7ejB7ej</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1CNi29Kg1CKg19Kg</t>
+          <t>0DKh29Kg0AKg09Kg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4770,12 +4770,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9YDJFX9H9XCHCX9H</t>
+          <t>Z34kf04kZ04kf04k</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:31</t>
+          <t>HDU checksum updated 2026-01-07T18:03:52</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:31</t>
+          <t>data unit checksum updated 2026-01-07T18:03:52</t>
         </is>
       </c>
     </row>
@@ -4832,41 +4832,49 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VISDALevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>SEQSTART</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>VISDALevel2HDUList</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4880,7 +4888,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4894,7 +4902,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4908,7 +4916,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4922,10 +4930,38 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Applied flat.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5156,12 +5192,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EIRaEHPYEHPaEHPY</t>
+          <t>DHRaEHOZDHOaDHOW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5215,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -6720,12 +6756,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZflUedlRZdlRddlR</t>
+          <t>ZelTddkRZdkRbdkR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6779,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7118,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DgMHEgJHDgJHDgJH</t>
+          <t>CiJJEfJGCfJGCfJG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7141,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7984,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U1o8a0m6X0m6a0m6</t>
+          <t>U0o7a0l6U0l6a0l6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8007,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8886,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EUafHUZdEUadEUWd</t>
+          <t>EWaeETWdETadETWd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8909,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -9118,12 +9154,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HCeLJ9ZJHAdJH9ZJ</t>
+          <t>GBdKJ9ZJGAbJG9ZJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9177,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9378,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6THB9T996TEA6T99</t>
+          <t>6VEA6S996SEA6S99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9401,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -866,12 +866,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7EcD79cD7EcD79cD</t>
+          <t>5FdF89aC5CaC59aC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>94LaA4La94LaA4La</t>
+          <t>ajcYahaYahaYahaY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3358544653</t>
+          <t>81622916</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mCA9nA58mAA8mA38</t>
+          <t>9SpFERoF9RoFCRoF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2524035719</t>
+          <t>1435927597</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>hZEikZ9hhZEhhZ9h</t>
+          <t>UDaFVBY9UBaCUBW9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2048992434</t>
+          <t>3583759094</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B9emC7ejB7ejB7ej</t>
+          <t>GAnlH2klG9klG9kl</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3784,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44499607</t>
+          <t>41878143</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0DKh29Kg0AKg09Kg</t>
+          <t>oCLip9IfoAIfo9If</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4770,12 +4770,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Z34kf04kZ04kf04k</t>
+          <t>lG3Tn93RlG3Rl93R</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:52</t>
+          <t>HDU checksum updated 2026-01-08T14:07:57</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:52</t>
+          <t>data unit checksum updated 2026-01-08T14:07:57</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2454833</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4882,16 +4882,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>2026-01-08T19:07:57.508</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4902,7 +4906,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4916,7 +4920,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4930,7 +4934,7 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4944,7 +4948,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied flat.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4958,10 +4962,24 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5192,12 +5210,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DHRaEHOZDHOaDHOW</t>
+          <t>CJPaCGNYCGNaCGNW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5233,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6774,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZelTddkRZdkRbdkR</t>
+          <t>YdjSadjRZdjRadjR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6797,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -7118,12 +7136,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CiJJEfJGCfJGCfJG</t>
+          <t>BhKICfHGBfHGBfHG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7159,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -7984,12 +8002,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U0o7a0l6U0l6a0l6</t>
+          <t>Yrm6aok6Sok6Yok6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8025,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -8886,12 +8904,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EWaeETWdETadETWd</t>
+          <t>CVadFTVdCTZdCTZd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8927,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9172,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GBdKJ9ZJGAbJG9ZJ</t>
+          <t>FAaJH9ZJFAaJF9YJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9195,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9396,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6VEA6S996SEA6S99</t>
+          <t>4UDB7S994SAA4S97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9419,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -866,12 +866,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5FdF89aC5CaC59aC</t>
+          <t>5GdF89aD5EaD59aD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ajcYahaYahaYahaY</t>
+          <t>ajcaaiaTaiaYaiaY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9SpFERoF9RoFCRoF</t>
+          <t>9SpIESoF9SoFCSoF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UDaFVBY9UBaCUBW9</t>
+          <t>UDaGVCY9UCaEUCW9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GAnlH2klG9klG9kl</t>
+          <t>GAnoH3klGAklG3kl</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>oCLip9IfoAIfo9If</t>
+          <t>oDLip9IgoCIgo9Ig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4770,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>lG3Tn93RlG3Rl93R</t>
+          <t>6DUF8ATD6ATD6ATD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:57</t>
+          <t>HDU checksum updated 2026-01-16T10:19:56</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:57</t>
+          <t>data unit checksum updated 2026-01-16T10:19:56</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-08T19:07:57.508</t>
+          <t>2026-01-16T17:19:56.779</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5210,12 +5210,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CJPaCGNYCGNaCGNW</t>
+          <t>CJPaCHNZCHNaCHNY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6774,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YdjSadjRZdjRadjR</t>
+          <t>YgjSadjSZdjSadjS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -7136,12 +7136,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BhKICfHGBfHGBfHG</t>
+          <t>BhKICgHHBgHHBgHH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yrm6aok6Sok6Yok6</t>
+          <t>Y2m9a0k6T0k6Y0k6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -8904,12 +8904,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CVadFTVdCTZdCTZd</t>
+          <t>CVagFUVdCUZdCUZd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -9172,12 +9172,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FAaJH9ZJFAaJF9YJ</t>
+          <t>FDaMH9ZJFAaJF9YJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -9396,12 +9396,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4UDB7S994SAA4S97</t>
+          <t>4UDC7T994TAA4T99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:57</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -866,12 +866,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5GdF89aD5EaD59aD</t>
+          <t>9FeE99eD9EeD99eD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ajcaaiaTaiaYaiaY</t>
+          <t>dkgZehdYdhdYdhdY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9SpIESoF9SoFCSoF</t>
+          <t>AU4GDR2FAR2FAR2F</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UDaGVCY9UCaEUCW9</t>
+          <t>XEgEZBZ9XBdEXBZ9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GAnoH3klGAklG3kl</t>
+          <t>JAomL3olJ9olJ9ol</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>oDLip9IgoCIgo9Ig</t>
+          <t>2DMh49Mg2AMg29Mg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4770,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6DUF8ATD6ATD6ATD</t>
+          <t>7DaFACSF9CYFACYF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:56</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:56</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-16T17:19:56.779</t>
+          <t>2026-01-16T22:40:10.134</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5210,12 +5210,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CJPaCHNZCHNaCHNY</t>
+          <t>FITaGHQYFHQaFHQY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6774,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YgjSadjSZdjSadjS</t>
+          <t>ZfnUhdmRZdmRfdmR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -7136,12 +7136,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BhKICgHHBgHHBgHH</t>
+          <t>EgLHGgLHEgLHEgLH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y2m9a0k6T0k6Y0k6</t>
+          <t>Y1q8a0n6Y0n6a0n6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -8904,12 +8904,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CVagFUVdCUZdCUZd</t>
+          <t>GUbfGUZdGUbdGUZd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -9172,12 +9172,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FDaMH9ZJFAaJF9YJ</t>
+          <t>IChLL9ZJIAfJI9ZJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -9396,12 +9396,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4UDC7T994TAA4T99</t>
+          <t>8TAB8TA98TAA8TA9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:57</t>
+          <t>HDU checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:57</t>
+          <t>data unit checksum updated 2026-01-16T15:40:10</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -18,10 +18,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext9" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext12" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext13" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,12 +488,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROI_TABLE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -507,12 +503,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEMP_TIME</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -527,7 +523,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -537,12 +533,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STAR_TABLE</t>
+          <t>VECTORS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -567,12 +563,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PIXEL_ROW</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -582,12 +578,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PIXEL_COLUMN</t>
+          <t>MODEL_IMAGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -597,75 +593,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>BACKGROUND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CompImageHDU</t>
-        </is>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ImageHDU</t>
-        </is>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CompImageHDU</t>
-        </is>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ImageHDU</t>
-        </is>
-      </c>
-      <c r="C15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -680,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,7 +659,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -745,7 +681,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -767,7 +703,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -780,10 +716,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -794,10 +734,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,7 +757,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -838,58 +782,472 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PIXEL_COLUMN</t>
-        </is>
-      </c>
+          <t>WCSAXES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PIXEL_COLUMN</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9FeE99eD9EeD99eD</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2758256725</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PC1_1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.32021358825394</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PC1_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.94734537413635</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-0.94734537413635</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-0.32021358825394</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEC--TAN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Declination, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>316.64517211914</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-49.964656829834</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-49.964656829834</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OAXAQ4V6O9VAO9V3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>695167502</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -904,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,12 +1295,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -959,17 +1317,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -981,17 +1339,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -1004,3048 +1362,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>BACKGROUND</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>BACKGROUND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ZR66fP65ZP65dP65</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TTYPE15</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>contamination</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>contamination</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TFORM15</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TTYPE16</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TFORM16</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TTYPE17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>total_in_aperture</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>total_in_aperture</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TFORM17</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>dkgZehdYdhdYdhdY</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
           <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>81622916</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Image extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>data type of original image</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dimension of original image</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NAXIS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DPOS0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460518789</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Change in position in Row from original WCS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DPOS1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Change in position in Column from original WCS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AU4GDR2FAR2FAR2F</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1435927597</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D78"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Image extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WCSAXES</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Number of coordinate axes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CRPIX1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CRPIX2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PC1_1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PC1_2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PC2_1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PC2_2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-0.00021666666666666</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CDELT2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.00021666666666667</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CUNIT2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>RA---TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CTYPE2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DEC--TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>45.460998535156</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CRVAL2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-16.594999313354</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-16.594999313354</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A_ORDER</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A_0_0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3.37003854432842e-18</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A_0_1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-6.9785263260057e-20</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A_0_2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-3.9703987595512e-23</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A_0_3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>6.66363813187626e-25</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A_1_0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.6079633451011e-05</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A_1_1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-8.2922292375176e-07</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A_1_2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-3.3183151069542e-10</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A_2_0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-5.6509448985679e-23</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A_2_1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1.22485736636324e-24</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A_3_0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-3.6017523652885e-10</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B_ORDER</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B_0_0</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0.000151435005371086</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B_0_1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.000544760966309224</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B_0_2</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.36516576587348e-05</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B_0_3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.09338166521394e-10</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B_1_0</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.54376528535914e-18</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B_1_1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3.52359242917892e-20</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B_1_2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-2.4342035926037e-23</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B_2_0</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.44813947783169e-05</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B_2_1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7.88636107165082e-11</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B_3_0</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-1.4166460599018e-23</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AP_ORDER</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AP_0_0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-3.3700385443284e-18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AP_0_1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>6.9785263260057e-20</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AP_0_2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>3.97039875955128e-23</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AP_0_3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>-6.6636381318762e-25</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AP_1_0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.60796334510111e-05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AP_1_1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>8.29222923751763e-07</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AP_1_2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>3.31831510695423e-10</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AP_2_0</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>5.65094489856793e-23</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AP_2_1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-1.2248573663632e-24</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AP_3_0</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3.60175236528857e-10</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BP_ORDER</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BP_0_0</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-0.00015143500537108</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BP_0_1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>-0.00054476096630922</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-1.3651657658734e-05</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-1.0933816652139e-10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>-1.5437652853591e-18</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>-3.5235924291789e-20</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2.43420359260379e-23</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-1.4481394778316e-05</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-7.8863610716508e-11</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1.4166460599018e-23</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>XEgEZBZ9XBdEXBZ9</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>3583759094</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>binary table extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>data type of original image</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dimension of original image</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NAXIS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of group parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>JAomL3olJ9olJ9ol</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>41878143</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Image extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NAXIS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>electrons/pixel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>data units: electrons/pixel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2DMh49Mg2AMg29Mg</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3483260417</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -4060,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4338,7 +1768,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v3.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4374,7 +1804,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4392,7 +1822,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/01/04/2026-01-04__14-54-31_VisSci_LTT_1445_A_d050_n026_f00050_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4428,7 +1858,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LTT_1445_A</t>
+          <t>HD_200654</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4446,7 +1876,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>45.46099853515625</t>
+          <t>316.64697265625</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4464,7 +1894,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-16.594999313354492</t>
+          <t>-49.965946197509766</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4482,7 +1912,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4500,7 +1930,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4518,7 +1948,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4554,7 +1984,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4572,7 +2002,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4590,7 +2020,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4608,7 +2038,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4626,7 +2056,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4644,7 +2074,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4734,7 +2164,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>820853698</t>
+          <t>840078298</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4752,7 +2182,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>503000000</t>
+          <t>706000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4770,12 +2200,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7DaFACSF9CYFACYF</t>
+          <t>nO5eoM2bnM2bnM2b</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>HDU checksum updated 2026-08-25T21:26:18</t>
         </is>
       </c>
     </row>
@@ -4793,20 +2223,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>data unit checksum updated 2026-08-25T21:26:18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.4.2</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4814,172 +2244,708 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Commanded roll [deg]</t>
-        </is>
-      </c>
+          <t>0.6.0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DPCSEQID</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DPC Obseravation Sequence ID</t>
-        </is>
-      </c>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2454833</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DPC Observation Sequence Start</t>
-        </is>
-      </c>
+          <t>VISDALevel2HDUList</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VISDALevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2026-08-26T01:26:18.893</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-16T22:40:10.134</t>
+          <t>316.6450976892217</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pandora DPC Processing Time</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>-49.964678241939716</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Executed DEC [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>108.69678158854717</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Executed roll [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>POSX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>1030.910864634688</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>X [column] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>POSY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>1029.9427911844318</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Y [row] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Gaia DR3 6477295296414847232</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Gaia DR3 source ID</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
+          <t>316.64613723994984</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Gaia DR3 RA in J2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GAIADEC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-49.96518470993648</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gaia DR3 DEC in J2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PARALLAX</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.621226952307976</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Gaia DR3 parallax</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PMRA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>193.953457454434</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmra</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PMDEC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-274.0404188035844</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmdec</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2MASSID</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2MASS J21063474-4957500</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2MASS source ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J_M</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7.648</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2MASS j magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>H_M</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7.252</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2MASS h magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>K_M</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7.154</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>G_M</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>8.88517868234036</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gaia DR3 g magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BP_M</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>9.245725468793857</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RP_M</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8.332176759726085</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TEFF</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Gaia DR3 Teff</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LOGG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Gaia DR3 logg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SRT_DATE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:04:21.706</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>File Start Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>END_DATE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:24:11.706</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>File End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FILETIME</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>19.83333333333345</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Time the file is observed for in minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VITLTIME</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>16.66666679084301</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Time VITL was on in minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ONTARG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>79.83193277310924</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Percentage On Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NKEEPOUT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>71.42857142857143</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Percentage of time NIRDA keepout obeyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VKEEPOUT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>52.94117647058824</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Percentage of time VISDA keepout obeyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VITLMISS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>N times VITL return missing data</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>APCOMP1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Aperture Completeness Metric 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TARGCENT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Target Centered</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TARGCOMP</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Target Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TARGTIME</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Usable Target Time is over 10 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Applied bias.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4992,7 +2958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5092,7 +3058,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5106,7 +3072,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5120,7 +3086,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5186,153 +3152,153 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2147483648</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2147483648</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>T7e5T4c4T4c4T4c4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FITaGHQYFHQaFHQY</t>
+          <t>525446840</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3451315978</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
-        </is>
-      </c>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>electrons/pixel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data units: electrons/pixel</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>1028.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>0.94734537413635</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.76604444311898</t>
+          <t>-0.94734537413635</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5344,13 +3310,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5362,1044 +3328,900 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.76604444311898</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.00021666666666666</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.00021666666666667</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RA---TAN-SIP</t>
+          <t>316.64517211914</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DEC--TAN-SIP</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.460998535156</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-16.594999313354</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-16.594999313354</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A_ORDER</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A_0_0</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.37003854432842e-18</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A_0_1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-6.9785263260057e-20</t>
+          <t>0.94734537413635</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A_0_2</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-3.9703987595512e-23</t>
+          <t>-0.94734537413635</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A_0_3</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6.66363813187626e-25</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A_1_0</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-1.6079633451011e-05</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A_1_1</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-8.2922292375176e-07</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A_1_2</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-3.3183151069542e-10</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A_2_0</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-5.6509448985679e-23</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A_2_1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.22485736636324e-24</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A_3_0</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-3.6017523652885e-10</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B_ORDER</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>316.64517211914</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B_0_0</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.000151435005371086</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B_0_1</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.000544760966309224</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B_0_2</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.36516576587348e-05</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B_0_3</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.09338166521394e-10</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B_1_0</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.54376528535914e-18</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B_1_1</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3.52359242917892e-20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B_1_2</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-2.4342035926037e-23</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B_2_0</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.44813947783169e-05</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B_2_1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7.88636107165082e-11</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B_3_0</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>-1.4166460599018e-23</t>
+          <t>0.94734537413635</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AP_ORDER</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-0.94734537413635</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AP_0_0</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>-3.3700385443284e-18</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AP_0_1</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6.9785263260057e-20</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AP_0_2</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.97039875955128e-23</t>
+          <t>0.00021750277777778</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AP_0_3</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-6.6636381318762e-25</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AP_1_0</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.60796334510111e-05</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AP_1_1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8.29222923751763e-07</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AP_1_2</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3.31831510695423e-10</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AP_2_0</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>5.65094489856793e-23</t>
+          <t>316.64517211914</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AP_2_1</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-1.2248573663632e-24</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AP_3_0</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3.60175236528857e-10</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BP_ORDER</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BP_0_0</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-0.00015143500537108</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BP_0_1</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-0.00054476096630922</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>-1.3651657658734e-05</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>-1.0933816652139e-10</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>-1.5437652853591e-18</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>-3.5235924291789e-20</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2.43420359260379e-23</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>-1.4481394778316e-05</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>-7.8863610716508e-11</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1.4166460599018e-23</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
@@ -6414,7 +4236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6447,17 +4269,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -6469,12 +4291,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6491,12 +4313,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6514,290 +4336,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Time frame is JD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>StarROI_StartX</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>StarROI_StartX</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>UeYlUZXjUbXjUZXj</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>I21</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I21</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TBCOL1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>StarROI_StartY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>StarROI_StartY</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>I21</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>I21</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TBCOL2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ROI_TABLE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ROI_TABLE</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NUMSTARS</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Number of star ROIs in datacube</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STARDIMS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Dimension (N) of ROIs used to capture each star</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ZfnUhdmRZdmRfdmR</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2007004370</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>2620499513</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -6812,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6845,17 +4497,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -6867,12 +4519,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6889,12 +4541,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6912,254 +4564,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>second</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Exposure time unit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ExposureStartTime_us</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ExposureStartTime_us</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>VgTZWZQYVdQYVZQY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>I194</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I194</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TBCOL1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TBCOL2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TEMP_TIME</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TEMP_TIME</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EgLHGgLHEgLHEgLH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2899297478</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>3501981725</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -7174,7 +4692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7207,17 +4725,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -7274,7 +4792,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7292,7 +4810,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7345,12 +4863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7367,12 +4885,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -7385,12 +4903,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -7398,17 +4916,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -7416,17 +4934,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Declination</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Declination</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -7434,17 +4952,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -7452,17 +4970,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -7470,7 +4988,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
+          <t>TTYPE4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7488,17 +5006,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TFORM3</t>
+          <t>TFORM4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -7506,17 +5024,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TBCOL3</t>
+          <t>TTYPE5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>PCOTemp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>PCOTemp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -7524,508 +5042,544 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFORM5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SDETMETH</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
-        </is>
-      </c>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ATAITIME</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>820853698.503</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TAI Time for ast soln</t>
+          <t>name of extension</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AIMMEAN</t>
+          <t>SDETMETH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>101.395988</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Image Mean after sigma clipping</t>
+          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AIMSTD</t>
+          <t>ATAITIME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.082717</t>
+          <t>840078298.706</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Image Standard Deviation after sigma clipping</t>
+          <t>TAI Time for ast soln</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ATHRESH1</t>
+          <t>AIMMEAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>112.849083</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1st Star Detection Threshold</t>
+          <t>Image Mean after sigma clipping</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ATHRESH2</t>
+          <t>AIMSTD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.010312</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2nd Star Detection Threshold</t>
+          <t>Image Standard Deviation after sigma clipping</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMINELLP</t>
+          <t>ATHRESH1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Minimum ellipticity threshold for stars</t>
+          <t>1st Star Detection Threshold</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMAXELLP</t>
+          <t>ATHRESH2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Maximum ellipticity threshold for stars</t>
+          <t>2nd Star Detection Threshold</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMINFLUX</t>
+          <t>AMINELLP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Minimum flux threshold for stars</t>
+          <t>Minimum ellipticity threshold for stars</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMAXFLUX</t>
+          <t>AMAXELLP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maximum flux threshold for stars</t>
+          <t>Maximum ellipticity threshold for stars</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AXAXFLIP</t>
+          <t>AMINFLUX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Was x-axis flipped for ast soln</t>
+          <t>Minimum flux threshold for stars</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASCAL</t>
+          <t>AMAXFLUX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7804</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Plate Scale for ast soln</t>
+          <t>Maximum flux threshold for stars</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASCALRMS</t>
+          <t>AXAXFLIP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Plate Scale RMS error for ast soln</t>
+          <t>Was x-axis flipped for ast soln</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AROT</t>
+          <t>ASCAL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>39.905</t>
+          <t>0.7889</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rotation for ast soln</t>
+          <t>Plate Scale for ast soln</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AROTRMS</t>
+          <t>ASCALRMS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rotation RMS error for ast soln</t>
+          <t>Plate Scale RMS error for ast soln</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>AROT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>45.46205</t>
+          <t>108.631</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Right Ascension for ast soln</t>
+          <t>Rotation for ast soln</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ARARMS</t>
+          <t>AROTRMS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9.699e-05</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Right Ascension RMS error for ast soln</t>
+          <t>Rotation RMS error for ast soln</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ADEC</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-16.594716</t>
+          <t>316.645807</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Declination for ast soln</t>
+          <t>Right Ascension for ast soln</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADECRMS</t>
+          <t>ARARMS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.00010624</t>
+          <t>6.443e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Declination RMS error for ast soln</t>
+          <t>Right Ascension RMS error for ast soln</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AZERP</t>
+          <t>ADEC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>-49.964709</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Magnitude Zeropoint for ast soln</t>
+          <t>Declination for ast soln</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AZERPRMS</t>
+          <t>ADECRMS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>9.975e-05</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Magnitude Zeropoint RMS error for ast soln</t>
+          <t>Declination RMS error for ast soln</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AQUADS</t>
+          <t>AZERP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Number of quads used for ast soln</t>
+          <t>Magnitude Zeropoint for ast soln</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AVERTS</t>
+          <t>AZERPRMS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Number of quad sides used for ast soln</t>
+          <t>Magnitude Zeropoint RMS error for ast soln</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APHSTARS</t>
+          <t>AQUADS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Number of photometric stars used for ast soln</t>
+          <t>Number of quads used for ast soln</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APOSTARS</t>
+          <t>AVERTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Number of position stars used for ast soln</t>
+          <t>Number of quad sides used for ast soln</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>APHSTARS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y1q8a0n6Y0n6a0n6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>Number of photometric stars used for ast soln</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>APOSTARS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3343168083</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>Number of position stars used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AlAFBj8FAjAFAj5F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2712404471</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -8073,17 +5627,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -8140,7 +5694,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8158,7 +5712,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8211,12 +5765,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8233,12 +5787,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>xCen</t>
+          <t>avg_ra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>xCen</t>
+          <t>avg_ra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -8251,12 +5805,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -8264,17 +5818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>avg_dec</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>avg_dec</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -8282,17 +5836,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yCen</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>yCen</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -8300,17 +5854,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>avg_rot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>avg_rot</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -8318,17 +5872,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -8336,17 +5890,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
+          <t>TTYPE4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>err_ra</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>err_ra</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -8354,17 +5908,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TFORM3</t>
+          <t>TFORM4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>I50</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I50</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -8372,17 +5926,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TBCOL3</t>
+          <t>TTYPE5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>err_dec</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>err_dec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -8390,17 +5944,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TTYPE4</t>
+          <t>TFORM5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ellipticity</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ellipticity</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -8408,17 +5962,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TFORM4</t>
+          <t>TTYPE6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>err_rot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>err_rot</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -8426,17 +5980,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TBCOL4</t>
+          <t>TFORM6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -8444,17 +5998,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TTYPE5</t>
+          <t>TTYPE7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NumPix</t>
+          <t>jd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NumPix</t>
+          <t>jd</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -8462,17 +6016,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TFORM5</t>
+          <t>TFORM7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I40</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I40</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -8480,17 +6034,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TBCOL5</t>
+          <t>TTYPE8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>exptime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>exptime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -8498,17 +6052,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TTYPE6</t>
+          <t>TFORM8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CatalogRA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CatalogRA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -8516,17 +6070,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TFORM6</t>
+          <t>TTYPE9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>target_sep</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>target_sep</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -8534,17 +6088,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TBCOL6</t>
+          <t>TFORM9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -8552,17 +6106,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTYPE7</t>
+          <t>TTYPE10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CatalogDec</t>
+          <t>vitl_frames_count</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CatalogDec</t>
+          <t>vitl_frames_count</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -8570,17 +6124,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TFORM7</t>
+          <t>TFORM10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -8588,17 +6142,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TBCOL7</t>
+          <t>TTYPE11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>vitl_missing_frames</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>vitl_missing_frames</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -8606,17 +6160,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TTYPE8</t>
+          <t>TFORM11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CatalogMag</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CatalogMag</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -8624,17 +6178,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TFORM8</t>
+          <t>TTYPE12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>earth_angle</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>earth_angle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -8642,17 +6196,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TBCOL8</t>
+          <t>TFORM12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -8660,17 +6214,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TTYPE9</t>
+          <t>TTYPE13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FittedRA</t>
+          <t>earth_illumination</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FittedRA</t>
+          <t>earth_illumination</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -8678,17 +6232,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TFORM9</t>
+          <t>TFORM13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -8696,17 +6250,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TBCOL9</t>
+          <t>TTYPE14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>sun_angle</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>sun_angle</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -8714,17 +6268,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TTYPE10</t>
+          <t>TFORM14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FittedDec</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FittedDec</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -8732,17 +6286,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TFORM10</t>
+          <t>TTYPE15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>visda_keepout</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>visda_keepout</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -8750,17 +6304,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TBCOL10</t>
+          <t>TFORM15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -8768,17 +6322,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TTYPE11</t>
+          <t>TTYPE16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FittedMag</t>
+          <t>nirda_keepout</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FittedMag</t>
+          <t>nirda_keepout</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -8786,17 +6340,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TFORM11</t>
+          <t>TFORM16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -8804,17 +6358,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TBCOL11</t>
+          <t>TTYPE17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>posx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>posx</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -8822,17 +6376,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TTYPE12</t>
+          <t>TFORM17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CatalogStar</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CatalogStar</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -8840,17 +6394,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TFORM12</t>
+          <t>TTYPE18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>posy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>posy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -8858,17 +6412,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TBCOL12</t>
+          <t>TFORM18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -8881,19 +6435,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>STAR_TABLE</t>
+          <t>VECTORS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>STAR_TABLE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8904,12 +6454,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GUbfGUZdGUbdGUZd</t>
+          <t>ZdSLadQKVdQKZdQK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -8922,12 +6472,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>912660790</t>
+          <t>2954309323</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -9042,7 +6592,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9060,7 +6610,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9172,12 +6722,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IChLL9ZJIAfJI9ZJ</t>
+          <t>eA6ng53leA3le53l</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -9190,12 +6740,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>215911647</t>
+          <t>43647640</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>
@@ -9210,7 +6760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9265,17 +6815,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -9297,7 +6847,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -9310,10 +6860,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9324,10 +6878,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9373,12 +6931,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PIXEL_ROW</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PIXEL_ROW</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9390,36 +6948,232 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>CONTAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8TAB8TA98TAA8TA9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:10</t>
+          <t>Flux not from the target in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>COMPLTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2333931600</t>
+          <t>1.0022219291335381</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:10</t>
+          <t>Fraction of flux from the target in aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1326397.5578262964</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Total flux expected in aperture in e/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>316.647026779318</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-49.965993163258695</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1030.1635671324907</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1031.0641774335984</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6477295296414847232</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GXIFHV9FGVGFGV9F</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15991026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:19</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -1224,12 +1224,12 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OAXAQ4V6O9VAO9V3</t>
+          <t>PAXAQ2W4P8W9P8W9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZR66fP65ZP65dP65</t>
+          <t>ZQ95gO64ZO64fO64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,12 +2200,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nO5eoM2bnM2bnM2b</t>
+          <t>YAYQc5VQZAVQa5VQ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:18</t>
+          <t>HDU checksum updated 2026-09-08T14:41:18</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:18</t>
+          <t>data unit checksum updated 2026-09-08T14:41:18</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:18.893</t>
+          <t>2026-09-08T18:41:18.832</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2880,44 +2880,56 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BKG10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>15.59</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10th percentile of Background</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BKG50</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>50th percentile of Background</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BKG90</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6824.330000000003</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>90th percentile of Background</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2928,7 +2940,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Appended Vectors.</t>
+          <t>Appended WCS.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2946,6 +2958,48 @@
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Applied bias.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3158,12 +3212,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T7e5T4c4T4c4T4c4</t>
+          <t>T4e5W4d3T4d3T4d3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:18</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3235,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:18</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4480,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UeYlUZXjUbXjUZXj</t>
+          <t>UcYkXZYiUaYiUYYi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4503,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -4654,12 +4708,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VgTZWZQYVdQYVZQY</t>
+          <t>WeTYWZRXWbRXWZRX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4731,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -5556,12 +5610,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AlAFBj8FAjAFAj5F</t>
+          <t>BkAEBi9EBiAEBi7E</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5633,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6508,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZdSLadQKVdQKZdQK</t>
+          <t>UcSKacRJWcRJacRJ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6531,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -6722,12 +6776,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eA6ng53leA3le53l</t>
+          <t>fA6mg34kfA4kf34k</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6799,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7204,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GXIFHV9FGVGFGV9F</t>
+          <t>HWBEHUAEHUAEHUAE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:19</t>
+          <t>HDU checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7227,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:19</t>
+          <t>data unit checksum updated 2026-09-08T14:41:19</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2_visda.xlsx
@@ -806,7 +806,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -824,7 +824,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -860,7 +860,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.94734537413635</t>
+          <t>-0.92528941038182</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -878,7 +878,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92528941038182</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1076,7 +1076,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PAXAQ2W4P8W9P8W9</t>
+          <t>O5aCQ5ZCO5aCO5WC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>695167502</t>
+          <t>825708307</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1452,12 +1452,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZQ95gO64ZO64fO64</t>
+          <t>GlTbJjSbGjSbGjSb</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>460518789</t>
+          <t>2867743191</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1858,7 +1858,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1876,7 +1876,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>316.64697265625</t>
+          <t>307.8599548339844</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1894,7 +1894,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-49.965946197509766</t>
+          <t>39.9389762878418</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1912,7 +1912,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1984,7 +1984,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2038,7 +2038,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>840078298</t>
+          <t>840068292</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2182,7 +2182,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>706000000</t>
+          <t>8000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,12 +2200,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YAYQc5VQZAVQa5VQ</t>
+          <t>6ddK9caI6caI6caI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:18</t>
+          <t>HDU checksum updated 2026-09-09T15:39:22</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:18</t>
+          <t>data unit checksum updated 2026-09-09T15:39:22</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:18.832</t>
+          <t>2026-09-09T19:39:22.758</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2310,7 +2310,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>316.6450976892217</t>
+          <t>307.86214468984406</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2328,7 +2328,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-49.964678241939716</t>
+          <t>39.93879672813656</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2346,7 +2346,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>108.69678158854717</t>
+          <t>247.71571592394164</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2364,7 +2364,7 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1030.910864634688</t>
+          <t>1030.7329142663189</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1029.9427911844318</t>
+          <t>1029.8410229048511</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2400,7 +2400,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gaia DR3 6477295296414847232</t>
+          <t>Gaia DR3 2064327278651198336</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2418,7 +2418,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>316.64613723994984</t>
+          <t>307.8599027970418</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2436,7 +2436,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-49.96518470993648</t>
+          <t>39.93891900336815</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.621226952307976</t>
+          <t>4.825836101438949</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2472,7 +2472,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>193.953457454434</t>
+          <t>16.716578051403854</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-274.0404188035844</t>
+          <t>20.96090596020299</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2508,7 +2508,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2MASS J21063474-4957500</t>
+          <t>2MASS J20312634+3956196</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2526,7 +2526,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7.648</t>
+          <t>7.458</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7.252</t>
+          <t>7.492</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2562,7 +2562,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>7.154</t>
+          <t>7.482</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2580,7 +2580,7 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8.88517868234036</t>
+          <t>7.5902658552584015</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9.245725468793857</t>
+          <t>7.594925828938212</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>8.332176759726085</t>
+          <t>7.552309075270038</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2634,7 +2634,7 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9951.392</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2652,7 +2652,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9497</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2664,198 +2664,198 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SRT_DATE</t>
+          <t>BKG10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-15T03:04:21.706</t>
+          <t>40.870000000000005</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>File Start Date</t>
+          <t>10th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>END_DATE</t>
+          <t>BKG50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-15T03:24:11.706</t>
+          <t>219.5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>File End Date</t>
+          <t>50th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FILETIME</t>
+          <t>BKG90</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>19.83333333333345</t>
+          <t>318.6800000000001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Time the file is observed for in minutes</t>
+          <t>90th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VITLTIME</t>
+          <t>SRT_DATE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>16.66666679084301</t>
+          <t>2026-08-15T00:17:35.008</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Time VITL was on in minutes</t>
+          <t>File Start Date</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ONTARG</t>
+          <t>END_DATE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>79.83193277310924</t>
+          <t>2026-08-15T00:57:15.008</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Percentage On Target</t>
+          <t>File End Date</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NKEEPOUT</t>
+          <t>FILETIME</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>71.42857142857143</t>
+          <t>39.66666666666674</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Percentage of time NIRDA keepout obeyed</t>
+          <t>Time the file is observed for in minutes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VKEEPOUT</t>
+          <t>VITLTIME</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>52.94117647058824</t>
+          <t>39.500000327825546</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Percentage of time VISDA keepout obeyed</t>
+          <t>Time VITL was on in minutes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VITLMISS</t>
+          <t>ONTARG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>N times VITL return missing data</t>
+          <t>Percentage On Target</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APCOMP1</t>
+          <t>NKEEPOUT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>47.89915966386555</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Aperture Completeness Metric 1</t>
+          <t>Percentage of time NIRDA keepout obeyed</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TARGCENT</t>
+          <t>VKEEPOUT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>21.84873949579832</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Target Centered</t>
+          <t>Percentage of time VISDA keepout obeyed</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TARGCOMP</t>
+          <t>VITLMISS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Target Complete</t>
+          <t>N times VITL return missing data</t>
         </is>
       </c>
     </row>
@@ -2880,54 +2880,54 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BKG10</t>
+          <t>APCOMP1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10th percentile of Background</t>
+          <t>Aperture Completeness Metric 1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BKG50</t>
+          <t>TARGCENT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>False</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>50th percentile of Background</t>
+          <t>Target Centered</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BKG90</t>
+          <t>TARGCOMP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6824.330000000003</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>90th percentile of Background</t>
+          <t>Target Complete</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -3212,12 +3212,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T4e5W4d3T4d3T4d3</t>
+          <t>RPDgTNAeRNAeRNAe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:18</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>525446840</t>
+          <t>2307185145</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:18</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3334,7 +3334,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.94734537413635</t>
+          <t>-0.92528941038182</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3352,7 +3352,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92528941038182</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3496,7 +3496,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3514,7 +3514,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3550,7 +3550,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3658,7 +3658,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3676,7 +3676,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.94734537413635</t>
+          <t>-0.92528941038182</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92528941038182</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3712,7 +3712,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3838,7 +3838,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3856,7 +3856,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3892,7 +3892,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4000,7 +4000,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4018,7 +4018,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.94734537413635</t>
+          <t>-0.92528941038182</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4036,7 +4036,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92528941038182</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4054,7 +4054,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.37926179221649</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4180,7 +4180,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4198,7 +4198,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4234,7 +4234,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4390,7 +4390,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4480,12 +4480,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UcYkXZYiUaYiUYYi</t>
+          <t>T7lpW7joT7joT7jo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2620499513</t>
+          <t>1105499181</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4708,12 +4708,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WeTYWZRXWbRXWZRX</t>
+          <t>LmfaMjZSLjfYLjZY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3501981725</t>
+          <t>2708996155</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5178,7 +5178,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>840078298.706</t>
+          <t>840068292.008</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5196,7 +5196,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>112.849083</t>
+          <t>189.042358</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.010312</t>
+          <t>19.295027</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5232,7 +5232,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5250,7 +5250,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5358,7 +5358,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.7889</t>
+          <t>0.7899</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5376,7 +5376,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5394,7 +5394,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>108.631</t>
+          <t>247.711</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5412,7 +5412,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5430,7 +5430,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>316.645807</t>
+          <t>307.860376</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.443e-05</t>
+          <t>8.489e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5466,7 +5466,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-49.964709</t>
+          <t>39.939956</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5484,7 +5484,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9.975e-05</t>
+          <t>6.817e-05</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5520,7 +5520,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5556,7 +5556,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5574,7 +5574,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5592,7 +5592,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5610,12 +5610,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BkAEBi9EBiAEBi7E</t>
+          <t>5hXSAfVS8fVSAfVS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -5628,12 +5628,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2712404471</t>
+          <t>3204105511</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6508,12 +6508,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UcSKacRJWcRJacRJ</t>
+          <t>YAASa45RZAARa33R</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2954309323</t>
+          <t>1316492219</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -6776,12 +6776,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fA6mg34kfA4kf34k</t>
+          <t>dA5ng93kdA3kd93k</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43647640</t>
+          <t>43451034</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0022219291335381</t>
+          <t>1.0017750354694497</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1326397.5578262964</t>
+          <t>6064568.043967242</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7062,7 +7062,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>316.647026779318</t>
+          <t>307.8599671153509</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -7076,7 +7076,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-49.965993163258695</t>
+          <t>39.93898083900071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -7090,7 +7090,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1030.1635671324907</t>
+          <t>1029.7930278378888</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -7104,7 +7104,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1031.0641774335984</t>
+          <t>1030.7358547975248</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6477295296414847232</t>
+          <t>2064327278651198336</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -7150,7 +7150,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7204,12 +7204,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HWBEHUAEHUAEHUAE</t>
+          <t>Fe3PIZ3MFd3MFZ3M</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:19</t>
+          <t>HDU checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
@@ -7222,12 +7222,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15991026</t>
+          <t>15335660</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:19</t>
+          <t>data unit checksum updated 2026-09-09T15:39:23</t>
         </is>
       </c>
     </row>
